--- a/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD3981E6-9058-431B-B395-3088322E6A43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B29B42C1-18DA-4430-B4C3-F16FA5CE2432}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A010180A-4871-40AA-B54B-41613F13BBF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{048FF934-0436-4BA2-BA9C-B2BD0A0E6FCF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8260361-F72A-499B-BB3D-CEEE93C9CA7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A35426-26A0-4B92-B341-666CBD750D18}"/>
 </file>